--- a/34th_Backgammon-championships_2b_output.xlsx
+++ b/34th_Backgammon-championships_2b_output.xlsx
@@ -767,11 +767,6 @@
           <t>5171975</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>5171868</t>
-        </is>
-      </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
           <t>5171797</t>
@@ -1053,47 +1048,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1123,7 +1117,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
@@ -1309,7 +1303,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
@@ -1397,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
@@ -1445,12 +1439,6 @@
       <c r="I9" t="n">
         <v>11</v>
       </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
       <c r="N9" t="n">
         <v>5</v>
       </c>
@@ -1565,7 +1553,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -1580,7 +1568,7 @@
         <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1608,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
@@ -1684,7 +1672,7 @@
         <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
         <v>5</v>
